--- a/data/gravel/Pashley Wildfinder 2025.xlsx
+++ b/data/gravel/Pashley Wildfinder 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B5F23A-5C26-F548-9E3F-BF9A835D6615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C284E6DA-FA42-374C-8F29-A19AFFB5EC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1540" yWindow="500" windowWidth="27260" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31480" yWindow="-16720" windowWidth="27260" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -362,7 +362,10 @@
     </r>
   </si>
   <si>
-    <t>usd</t>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>https://www.pashley.co.uk/cdn/shop/files/thumbnail_PashleyWildfinderRedside2040x2040_700x.jpg?v=1756388923</t>
   </si>
 </sst>
 </file>
@@ -815,6 +818,11 @@
         <v>79</v>
       </c>
     </row>
+    <row r="6" spans="1:8">
+      <c r="B6" t="s">
+        <v>106</v>
+      </c>
+    </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Pashley Wildfinder 2025.xlsx
+++ b/data/gravel/Pashley Wildfinder 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C284E6DA-FA42-374C-8F29-A19AFFB5EC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79E9555-0E82-7B48-A689-1895308477EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31480" yWindow="-16720" windowWidth="27260" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11120" yWindow="1220" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -366,6 +366,12 @@
   </si>
   <si>
     <t>https://www.pashley.co.uk/cdn/shop/files/thumbnail_PashleyWildfinderRedside2040x2040_700x.jpg?v=1756388923</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Stratford-upon-Avon, England</t>
   </si>
 </sst>
 </file>
@@ -772,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1697,6 +1703,14 @@
         <v>105</v>
       </c>
     </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>107</v>
+      </c>
+      <c r="B76" t="s">
+        <v>108</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Pashley Wildfinder 2025.xlsx
+++ b/data/gravel/Pashley Wildfinder 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79E9555-0E82-7B48-A689-1895308477EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C8ADFB-EDE6-6E43-9D03-B31A078479DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11120" yWindow="1220" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -372,6 +372,24 @@
   </si>
   <si>
     <t>Stratford-upon-Avon, England</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -778,7 +796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1531,183 +1549,213 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54">
-        <v>31.6</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>45</v>
-      </c>
-      <c r="B55" s="1"/>
+        <v>112</v>
+      </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>46</v>
-      </c>
-      <c r="B56">
-        <v>42</v>
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>47</v>
+        <v>114</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>48</v>
-      </c>
-      <c r="B58">
-        <v>180</v>
+        <v>42</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>49</v>
-      </c>
-      <c r="B59">
-        <v>160</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B60">
+        <v>31.6</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>51</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>101</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B61" s="1"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>75</v>
+        <v>46</v>
+      </c>
+      <c r="B62">
+        <v>42</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>53</v>
-      </c>
-      <c r="B63" s="1"/>
+        <v>47</v>
+      </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="B64">
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>56</v>
-      </c>
-      <c r="B66">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>58</v>
-      </c>
-      <c r="B68" s="1">
-        <v>3</v>
+        <v>52</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>59</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>70</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B69" s="1"/>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>60</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>61</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>70</v>
+        <v>55</v>
+      </c>
+      <c r="B71">
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B72">
-        <v>2595</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>63</v>
-      </c>
-      <c r="B73">
-        <v>4195</v>
+        <v>57</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>64</v>
-      </c>
-      <c r="B74" s="1"/>
+        <v>58</v>
+      </c>
+      <c r="B74" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
+        <v>60</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>61</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B78">
+        <v>2595</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>63</v>
+      </c>
+      <c r="B79">
+        <v>4195</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>64</v>
+      </c>
+      <c r="B80" s="1"/>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>65</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
         <v>107</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B82" t="s">
         <v>108</v>
       </c>
     </row>

--- a/data/gravel/Pashley Wildfinder 2025.xlsx
+++ b/data/gravel/Pashley Wildfinder 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C8ADFB-EDE6-6E43-9D03-B31A078479DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3F5910-A449-C146-915A-F6AA9F22C80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11240" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="117">
   <si>
     <t>brand</t>
   </si>
@@ -339,9 +339,6 @@
   </si>
   <si>
     <t>external</t>
-  </si>
-  <si>
-    <t>a8:g35</t>
   </si>
   <si>
     <t>threaded</t>
@@ -390,6 +387,15 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:g37</t>
   </si>
 </sst>
 </file>
@@ -796,7 +802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -844,7 +850,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="B6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -852,7 +858,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1063,7 +1069,7 @@
         <v>74.5</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -1086,7 +1092,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1109,7 +1115,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
         <v>73</v>
       </c>
@@ -1132,7 +1138,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
         <v>78</v>
       </c>
@@ -1155,7 +1161,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -1178,7 +1184,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
         <v>74</v>
       </c>
@@ -1188,7 +1194,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -1198,7 +1204,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -1218,488 +1224,511 @@
         <v>483</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
-      <c r="A25" t="s">
+    <row r="25" spans="1:7">
+      <c r="A25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0</v>
+      </c>
+      <c r="D25" s="6">
+        <v>0</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0</v>
+      </c>
+      <c r="F25" s="6">
+        <v>0</v>
+      </c>
+      <c r="G25" s="6"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0</v>
+      </c>
+      <c r="D26" s="6">
+        <v>0</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0</v>
+      </c>
+      <c r="F26" s="6">
+        <v>0</v>
+      </c>
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" t="s">
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" t="s">
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
-      <c r="A28" t="s">
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
-      <c r="A29" t="s">
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
         <v>24</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B31" t="s">
         <v>24</v>
       </c>
-      <c r="C29">
+      <c r="C31">
         <v>700</v>
       </c>
-      <c r="D29">
+      <c r="D31">
         <v>700</v>
       </c>
-      <c r="E29">
+      <c r="E31">
         <v>700</v>
       </c>
-      <c r="F29">
+      <c r="F31">
         <v>700</v>
       </c>
-      <c r="G29">
+      <c r="G31">
         <v>700</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
-      <c r="A30" t="s">
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
         <v>25</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B32" t="s">
         <v>25</v>
       </c>
-      <c r="C30">
+      <c r="C32">
         <v>42</v>
       </c>
-      <c r="D30">
+      <c r="D32">
         <v>42</v>
       </c>
-      <c r="E30">
+      <c r="E32">
         <v>42</v>
       </c>
-      <c r="F30">
+      <c r="F32">
         <v>42</v>
       </c>
-      <c r="G30">
+      <c r="G32">
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
-      <c r="A31" t="s">
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
         <v>26</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B33" t="s">
         <v>26</v>
       </c>
-      <c r="C31">
+      <c r="C33">
         <v>45</v>
       </c>
-      <c r="D31">
+      <c r="D33">
         <v>45</v>
       </c>
-      <c r="E31">
+      <c r="E33">
         <v>45</v>
       </c>
-      <c r="F31">
+      <c r="F33">
         <v>45</v>
       </c>
-      <c r="G31">
+      <c r="G33">
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
-      <c r="A32" t="s">
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
         <v>27</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B34" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="3">
-        <f>C34</f>
+      <c r="C34" s="3">
+        <f>C36</f>
         <v>155</v>
       </c>
-      <c r="D32" s="3">
-        <f>AVERAGE(D34,C35)</f>
+      <c r="D34" s="3">
+        <f>AVERAGE(D36,C37)</f>
         <v>161</v>
       </c>
-      <c r="E32" s="3">
-        <f t="shared" ref="E32:G32" si="0">AVERAGE(E34,D35)</f>
+      <c r="E34" s="3">
+        <f t="shared" ref="E34:G34" si="0">AVERAGE(E36,D37)</f>
         <v>171</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F34" s="3">
         <f t="shared" si="0"/>
         <v>181</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G34" s="3">
         <f t="shared" si="0"/>
         <v>189</v>
       </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" t="s">
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
         <v>28</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B35" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="3">
-        <f>D32</f>
+      <c r="C35" s="3">
+        <f>D34</f>
         <v>161</v>
       </c>
-      <c r="D33" s="3">
-        <f t="shared" ref="D33:F33" si="1">E32</f>
+      <c r="D35" s="3">
+        <f t="shared" ref="D35:F35" si="1">E34</f>
         <v>171</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E35" s="3">
         <f t="shared" si="1"/>
         <v>181</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F35" s="3">
         <f t="shared" si="1"/>
         <v>189</v>
       </c>
-      <c r="G33" s="3">
-        <f t="shared" ref="G33" si="2">G35</f>
+      <c r="G35" s="3">
+        <f t="shared" ref="G35" si="2">G37</f>
         <v>196</v>
       </c>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" s="1" t="s">
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C34">
+      <c r="C36">
         <v>155</v>
       </c>
-      <c r="D34">
+      <c r="D36">
         <v>160</v>
       </c>
-      <c r="E34">
+      <c r="E36">
         <v>170</v>
       </c>
-      <c r="F34">
+      <c r="F36">
         <v>180</v>
       </c>
-      <c r="G34">
+      <c r="G36">
         <v>188</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
-      <c r="A35" s="1" t="s">
+    <row r="37" spans="1:9">
+      <c r="A37" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C35">
+      <c r="C37">
         <v>162</v>
       </c>
-      <c r="D35">
+      <c r="D37">
         <v>172</v>
       </c>
-      <c r="E35">
+      <c r="E37">
         <v>182</v>
       </c>
-      <c r="F35">
+      <c r="F37">
         <v>190</v>
       </c>
-      <c r="G35">
+      <c r="G37">
         <v>196</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" t="s">
-        <v>29</v>
-      </c>
-      <c r="B37" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-    </row>
     <row r="38" spans="1:9">
-      <c r="A38" t="s">
-        <v>66</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>67</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>104</v>
+        <v>29</v>
+      </c>
+      <c r="B39" t="s">
+        <v>30</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
       <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>68</v>
-      </c>
-      <c r="B40" t="s">
-        <v>69</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>99</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>32</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
+      </c>
+      <c r="B42" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>34</v>
-      </c>
-      <c r="B44">
-        <v>61</v>
+        <v>32</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>35</v>
-      </c>
-      <c r="B45">
-        <v>2.8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B46">
-        <v>100</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="1"/>
+        <v>35</v>
+      </c>
+      <c r="B47">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="B48">
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>39</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B49" s="1"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50">
-        <v>148</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51">
-        <v>110</v>
+        <v>39</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>109</v>
+        <v>40</v>
+      </c>
+      <c r="B52">
+        <v>148</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53">
         <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>43</v>
+        <v>113</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60">
-        <v>31.6</v>
+        <v>42</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="1"/>
+        <v>43</v>
+      </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B62">
-        <v>42</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>47</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B63" s="1"/>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B64">
-        <v>180</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>49</v>
-      </c>
-      <c r="B65">
-        <v>160</v>
+        <v>47</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>50</v>
+        <v>48</v>
+      </c>
+      <c r="B66">
+        <v>180</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>51</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>101</v>
+        <v>49</v>
+      </c>
+      <c r="B67">
+        <v>160</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>52</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>53</v>
-      </c>
-      <c r="B69" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>54</v>
+        <v>52</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>55</v>
-      </c>
-      <c r="B71">
-        <v>2</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B71" s="1"/>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>56</v>
-      </c>
-      <c r="B72">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>57</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>70</v>
+        <v>55</v>
+      </c>
+      <c r="B73">
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>58</v>
-      </c>
-      <c r="B74" s="1">
-        <v>3</v>
+        <v>56</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>70</v>
@@ -1707,15 +1736,15 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>60</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>70</v>
+        <v>58</v>
+      </c>
+      <c r="B76" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>70</v>
@@ -1723,40 +1752,56 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>62</v>
-      </c>
-      <c r="B78">
-        <v>2595</v>
+        <v>60</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>63</v>
-      </c>
-      <c r="B79">
-        <v>4195</v>
+        <v>61</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>64</v>
-      </c>
-      <c r="B80" s="1"/>
+        <v>62</v>
+      </c>
+      <c r="B80">
+        <v>2595</v>
+      </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>65</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>105</v>
+        <v>63</v>
+      </c>
+      <c r="B81">
+        <v>4195</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
+        <v>64</v>
+      </c>
+      <c r="B82" s="1"/>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>65</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" t="s">
+        <v>106</v>
+      </c>
+      <c r="B84" t="s">
         <v>107</v>
-      </c>
-      <c r="B82" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Pashley Wildfinder 2025.xlsx
+++ b/data/gravel/Pashley Wildfinder 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3F5910-A449-C146-915A-F6AA9F22C80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9979ABC1-CAF4-A04C-B150-C9666E5D3D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11240" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1240,7 +1240,9 @@
       <c r="F25" s="6">
         <v>0</v>
       </c>
-      <c r="G25" s="6"/>
+      <c r="G25" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
@@ -1258,7 +1260,9 @@
       <c r="F26" s="6">
         <v>0</v>
       </c>
-      <c r="G26" s="6"/>
+      <c r="G26" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
